--- a/CanaryBanana/site/Practica_TDH_CanaryBanana.xlsx
+++ b/CanaryBanana/site/Practica_TDH_CanaryBanana.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupstucom-my.sharepoint.com/personal/llorenc_huguet_365_stucom_com/Documents/Documentos/GitHub/Digitalizacion/CanaryBanana/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{317634CD-0B97-4D36-81E2-096C1032478D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6DFD55-311B-4C6F-9F0F-2D4A93FEEBE6}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{317634CD-0B97-4D36-81E2-096C1032478D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79D1BA8C-CB5B-4AA0-BA49-16E87E966999}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividad_TDH" sheetId="2" r:id="rId1"/>
-    <sheet name="Listas" sheetId="1" state="hidden" r:id="rId2"/>
-    <sheet name="SOLUCIONES" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Listas" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>Tipo</t>
   </si>
@@ -257,12 +256,6 @@
   </si>
   <si>
     <t>Fase 5 – Ecosistema digital avanzado</t>
-  </si>
-  <si>
-    <t>Resultado Correcto</t>
-  </si>
-  <si>
-    <t>Impacto Correcto</t>
   </si>
   <si>
     <t xml:space="preserve">INSTRUCCIONES:
@@ -329,7 +322,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -374,6 +367,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -671,7 +668,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="110" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -700,6 +697,9 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
+      <c r="E3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
@@ -708,6 +708,9 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
+      <c r="E4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
@@ -716,6 +719,9 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
+      <c r="E5" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
@@ -724,6 +730,9 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
+      <c r="E6" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -732,6 +741,9 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
@@ -740,6 +752,9 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
+      <c r="E8" s="5">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
@@ -748,6 +763,9 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
+      <c r="E9" s="5">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
@@ -756,6 +774,9 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
+      <c r="E10" s="5">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
@@ -764,6 +785,9 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
+      <c r="E11" s="5">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
@@ -772,6 +796,9 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
+      <c r="E12" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
@@ -780,6 +807,9 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
+      <c r="E13" s="5">
+        <v>11</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
@@ -788,6 +818,9 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
+      <c r="E14" s="5">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
@@ -796,6 +829,9 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
+      <c r="E15" s="5">
+        <v>13</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
@@ -804,6 +840,9 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
+      <c r="E16" s="5">
+        <v>14</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
@@ -812,6 +851,9 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
+      <c r="E17" s="5">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
@@ -820,6 +862,9 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
+      <c r="E18" s="5">
+        <v>16</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
@@ -828,6 +873,9 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
+      <c r="E19" s="5">
+        <v>17</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
@@ -836,6 +884,9 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
+      <c r="E20" s="5">
+        <v>18</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
@@ -844,6 +895,9 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
+      <c r="E21" s="5">
+        <v>19</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
@@ -852,6 +906,9 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
+      <c r="E22" s="5">
+        <v>20</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
@@ -860,6 +917,9 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
+      <c r="E23" s="5">
+        <v>21</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
@@ -868,6 +928,9 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
+      <c r="E24" s="5">
+        <v>22</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
@@ -876,6 +939,9 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
+      <c r="E25" s="5">
+        <v>23</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
@@ -884,6 +950,9 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
+      <c r="E26" s="5">
+        <v>24</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
@@ -892,6 +961,9 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
+      <c r="E27" s="5">
+        <v>25</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
@@ -900,6 +972,9 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
+      <c r="E28" s="5">
+        <v>26</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
@@ -908,7 +983,9 @@
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="5">
+        <v>27</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
@@ -917,7 +994,9 @@
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="5">
+        <v>28</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
@@ -926,7 +1005,9 @@
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="5">
+        <v>29</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
@@ -935,7 +1016,9 @@
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="5">
+        <v>30</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
@@ -944,7 +1027,9 @@
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="5">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -962,6 +1047,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -1011,10 +1097,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1022,10 +1108,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1033,10 +1119,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1044,34 +1130,34 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1079,548 +1165,93 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B22">
+    <sortCondition ref="B2:B22"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/CanaryBanana/site/Practica_TDH_CanaryBanana.xlsx
+++ b/CanaryBanana/site/Practica_TDH_CanaryBanana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupstucom-my.sharepoint.com/personal/llorenc_huguet_365_stucom_com/Documents/Documentos/GitHub/Digitalizacion/CanaryBanana/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{317634CD-0B97-4D36-81E2-096C1032478D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79D1BA8C-CB5B-4AA0-BA49-16E87E966999}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{317634CD-0B97-4D36-81E2-096C1032478D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAE993F0-2183-45C6-9483-BAD52E6AE337}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividad_TDH" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
   <si>
     <t>Tipo</t>
   </si>
@@ -367,10 +367,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -659,14 +655,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="4" width="45" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="110" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>74</v>
       </c>
@@ -675,7 +671,7 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,18 +686,24 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="B3" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
         <v>44</v>
@@ -712,7 +714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
         <v>45</v>
@@ -723,7 +725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" t="s">
         <v>46</v>
@@ -734,7 +736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" t="s">
         <v>47</v>
@@ -745,7 +747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" t="s">
         <v>48</v>
@@ -756,7 +758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" t="s">
         <v>49</v>
@@ -767,7 +769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
         <v>50</v>
@@ -778,7 +780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
         <v>51</v>
@@ -789,7 +791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
         <v>52</v>
@@ -800,7 +802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" t="s">
         <v>53</v>
@@ -811,7 +813,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" t="s">
         <v>54</v>
@@ -822,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" t="s">
         <v>55</v>
@@ -833,7 +835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" t="s">
         <v>56</v>
@@ -844,7 +846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" t="s">
         <v>57</v>
@@ -855,7 +857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" t="s">
         <v>58</v>
@@ -866,7 +868,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" t="s">
         <v>59</v>
@@ -877,7 +879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" t="s">
         <v>60</v>
@@ -888,7 +890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" t="s">
         <v>61</v>
@@ -899,7 +901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
         <v>62</v>
@@ -910,7 +912,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
         <v>63</v>
@@ -921,7 +923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" t="s">
         <v>64</v>
@@ -932,7 +934,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" t="s">
         <v>65</v>
@@ -943,7 +945,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" t="s">
         <v>66</v>
@@ -954,7 +956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" t="s">
         <v>67</v>
@@ -965,7 +967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" t="s">
         <v>68</v>
@@ -976,18 +978,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="3"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="B29" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="E29" s="5">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
         <v>70</v>
@@ -998,7 +1004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
         <v>71</v>
@@ -1009,7 +1015,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
         <v>72</v>
@@ -1020,7 +1026,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="4" t="s">
         <v>73</v>
@@ -1078,13 +1084,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="56.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1095,7 +1101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>24</v>
       </c>
@@ -1103,7 +1109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1114,7 +1120,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1125,7 +1131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>35</v>
       </c>
@@ -1144,7 +1150,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>39</v>
       </c>
@@ -1152,7 +1158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>33</v>
       </c>
@@ -1160,7 +1166,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>20</v>
       </c>
@@ -1168,7 +1174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>36</v>
       </c>
@@ -1176,7 +1182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>14</v>
       </c>
@@ -1184,7 +1190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -1192,7 +1198,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>30</v>
       </c>
@@ -1200,7 +1206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>26</v>
       </c>
@@ -1208,42 +1214,42 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>9</v>
       </c>
